--- a/artfynd/A 5639-2022 artfynd.xlsx
+++ b/artfynd/A 5639-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,261 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134604231</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gamla Ekhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570579</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6332856</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant vid grotupplag</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karin Martinsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134603516</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5437</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gamla Ekhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570629</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6332810</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant vid naturminnesek.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>kirskål</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Aegopodium podagraria</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Aegopodium podagraria</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karin Martinsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5639-2022 artfynd.xlsx
+++ b/artfynd/A 5639-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2249597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62615290</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134604231</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1171,8 +1191,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134603516</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>